--- a/ValueSet-resq-stroke-discharge-section-code-vs.xlsx
+++ b/ValueSet-resq-stroke-discharge-section-code-vs.xlsx
@@ -9,12 +9,13 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
     <sheet name="Include #1" r:id="rId5" sheetId="3"/>
+    <sheet name="Include #2" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="74">
   <si>
     <t>Property</t>
   </si>
@@ -31,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T10:11:46+00:00</t>
+    <t>2026-09-23T10:52:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -103,6 +104,24 @@
     <t>Concept</t>
   </si>
   <si>
+    <t>75310-3</t>
+  </si>
+  <si>
+    <t>Health concerns document</t>
+  </si>
+  <si>
+    <t>48765-2</t>
+  </si>
+  <si>
+    <t>Allergies and adverse reactions document</t>
+  </si>
+  <si>
+    <t>46240-8</t>
+  </si>
+  <si>
+    <t>History of hospitalization and outpatient visits</t>
+  </si>
+  <si>
     <t>67851-6</t>
   </si>
   <si>
@@ -112,13 +131,7 @@
     <t>11329-0</t>
   </si>
   <si>
-    <t>History of general health Narrative</t>
-  </si>
-  <si>
-    <t>11450-4</t>
-  </si>
-  <si>
-    <t>Problem list - Reported</t>
+    <t>History of general health narrative</t>
   </si>
   <si>
     <t>8648-8</t>
@@ -130,13 +143,13 @@
     <t>11535-2</t>
   </si>
   <si>
-    <t>Hospital discharge diagnosis Narrative</t>
+    <t>Hospital discharge diagnosis note</t>
   </si>
   <si>
     <t>10185-7</t>
   </si>
   <si>
-    <t>Hospital discharge procedures</t>
+    <t>Hospital discharge procedure note</t>
   </si>
   <si>
     <t>87232-5</t>
@@ -148,7 +161,13 @@
     <t>30954-2</t>
   </si>
   <si>
-    <t>Relevant diagnostic tests/laboratory data Narrative</t>
+    <t>Relevant diagnostic tests and laboratory data note</t>
+  </si>
+  <si>
+    <t>8650-4</t>
+  </si>
+  <si>
+    <t>Hospital discharge disposition note</t>
   </si>
   <si>
     <t>8716-3</t>
@@ -157,22 +176,22 @@
     <t>Vital signs note</t>
   </si>
   <si>
+    <t>29545-1</t>
+  </si>
+  <si>
+    <t>Physical findings</t>
+  </si>
+  <si>
     <t>47420-5</t>
   </si>
   <si>
     <t>Functional status assessment note</t>
   </si>
   <si>
-    <t>8650-4</t>
-  </si>
-  <si>
-    <t>Hospital discharge disposition note</t>
-  </si>
-  <si>
     <t>75311-1</t>
   </si>
   <si>
-    <t>Discharge medications Narrative</t>
+    <t>Discharge medications note</t>
   </si>
   <si>
     <t>18776-5</t>
@@ -197,6 +216,27 @@
   </si>
   <si>
     <t>http://qualityregistry.org/CodeSystem/stroke-discharge-summary-section-cs</t>
+  </si>
+  <si>
+    <t>1184586001</t>
+  </si>
+  <si>
+    <t>Medical device document section</t>
+  </si>
+  <si>
+    <t>248326004</t>
+  </si>
+  <si>
+    <t>Anthropometric measure</t>
+  </si>
+  <si>
+    <t>866144008</t>
+  </si>
+  <si>
+    <t>Encounter note</t>
+  </si>
+  <si>
+    <t>http://snomed.info/sct</t>
   </si>
 </sst>
 </file>
@@ -460,7 +500,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -584,15 +624,39 @@
         <v>55</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -619,26 +683,88 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>60</v>
+        <v>66</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-resq-stroke-discharge-section-code-vs.xlsx
+++ b/ValueSet-resq-stroke-discharge-section-code-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T10:52:36+00:00</t>
+    <t>2026-09-23T10:52:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-resq-stroke-discharge-section-code-vs.xlsx
+++ b/ValueSet-resq-stroke-discharge-section-code-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T10:52:57+00:00</t>
+    <t>2026-10-14T14:44:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-resq-stroke-discharge-section-code-vs.xlsx
+++ b/ValueSet-resq-stroke-discharge-section-code-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T14:44:50+00:00</t>
+    <t>2026-10-15T10:29:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-resq-stroke-discharge-section-code-vs.xlsx
+++ b/ValueSet-resq-stroke-discharge-section-code-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T10:29:33+00:00</t>
+    <t>2026-10-19T07:01:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-resq-stroke-discharge-section-code-vs.xlsx
+++ b/ValueSet-resq-stroke-discharge-section-code-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T07:01:38+00:00</t>
+    <t>2026-10-28T15:45:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
